--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62813349</v>
+        <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>93493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örberga 0250/5550, Nrk</t>
+          <t>Hylletorp, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501851</v>
+        <v>501809</v>
       </c>
       <c r="R2" t="n">
-        <v>6538008</v>
+        <v>6538093</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-07-19</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-07-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ca 7 stänglar</t>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,25 +778,459 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Stenblock i tät barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Emelie Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Emelie Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311745</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137311867</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93493</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hylletorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>501849</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6538075</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emelie Olsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emelie Olsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311867</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137311722</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hylletorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>501766</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6538082</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emelie Olsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emelie Olsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311722</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137311827</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8459</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hylletorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>501819</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6538075</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emelie Olsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emelie Olsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137311827</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>62813349</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örberga 0250/5550, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>501851</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6538008</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Askersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lerbäck</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1995-07-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>1995-07-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ca 7 stänglar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Stenblock i tät barrskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/62813349</t>
         </is>
@@ -797,6 +1239,10 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1509-2022 artfynd.xlsx
+++ b/artfynd/S 1509-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137311745</v>
       </c>
       <c r="B2" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>137311867</v>
       </c>
       <c r="B3" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
